--- a/images/4runner/4Wannuh.xlsx
+++ b/images/4runner/4Wannuh.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="168">
   <si>
     <t>MODS</t>
   </si>
@@ -202,115 +202,67 @@
     <t>drill bit + hole punch</t>
   </si>
   <si>
-    <t>Y-pipe</t>
-  </si>
-  <si>
-    <t>0 (420) - 700</t>
+    <t>Y-pipe (700)</t>
   </si>
   <si>
     <t>battery cleaner</t>
   </si>
   <si>
-    <t>ANTIDOTE Roof rack full length (600-400, sold rhino roof rack)</t>
+    <t>ANTIDOTE Roof rack full length (worth 600, -400 sold rhino roof rack)</t>
   </si>
   <si>
     <t xml:space="preserve">grease + crowfoot + PB + silicone </t>
   </si>
   <si>
-    <t>OE Sliders</t>
-  </si>
-  <si>
-    <t>0 (200) - 750</t>
+    <t>OE Sliders (750) paid 200, -200 sold old sliders</t>
   </si>
   <si>
     <t>wd40, clamps, bungee</t>
   </si>
   <si>
-    <t>Diode Dyamic SSD pro fog lights</t>
-  </si>
-  <si>
-    <t>0 (150) - 500</t>
+    <t>Diode Dyamic SSD pro fog lights (500), paid 150, -150 sold old lights</t>
   </si>
   <si>
     <t>grease gun + grease</t>
   </si>
   <si>
-    <t>Front runner awning</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>(500 tot)</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve"> - 250</t>
-    </r>
+    <t>Front runner awning (250) paid 100, -100 sold stuff</t>
   </si>
   <si>
     <t>oil change 12/18/25</t>
   </si>
   <si>
-    <t>Baja S1</t>
-  </si>
-  <si>
-    <t>0-250</t>
+    <t>Baja S1 (250) paid 100, -100 sold stuff</t>
   </si>
   <si>
     <t>R-diff  69500 miles 1/24/26</t>
   </si>
   <si>
-    <t xml:space="preserve">S1 mounts </t>
-  </si>
-  <si>
-    <t>0 - 50</t>
+    <t>S1 mounts (50) paid 25, -25 sold stuff</t>
   </si>
   <si>
     <t>cabin air filter</t>
   </si>
   <si>
-    <t>Trigger 4 plus</t>
-  </si>
-  <si>
-    <t>0 - 360</t>
+    <t>Trigger 4 plus (360) paid 100, -100 sold stuff</t>
   </si>
   <si>
     <t>windshield repair</t>
   </si>
   <si>
-    <t>Compressor mount</t>
-  </si>
-  <si>
-    <t>0 - 135</t>
+    <t>Compressor mount (135) paid 100, -100 sold stuff</t>
   </si>
   <si>
     <t>brake cleaners</t>
   </si>
   <si>
-    <t xml:space="preserve"> ARB compressor </t>
+    <t xml:space="preserve"> ARB compressor (360) paid 50, -50 sold stuff</t>
   </si>
   <si>
     <t>oil change 2/11/26</t>
   </si>
   <si>
-    <t>Rear molle left</t>
-  </si>
-  <si>
-    <t>0 - 160</t>
+    <t>Rear molle left (160) paid 25, -25 sold stuff</t>
   </si>
   <si>
     <t>T-case &amp; F-diff 3/6/26 @ 72K</t>
@@ -880,7 +832,7 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2">
         <f>SUM(B3:B1003)</f>
-        <v>17542</v>
+        <v>17962</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -1296,11 +1248,11 @@
       <c r="A34" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="2">
+        <v>420.0</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E34" s="2">
         <v>4.0</v>
@@ -1308,13 +1260,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" s="2">
         <v>200.0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E35" s="2">
         <v>40.0</v>
@@ -1322,13 +1274,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="E36" s="2">
         <v>18.0</v>
@@ -1336,13 +1288,13 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.0</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E37" s="2">
         <v>32.0</v>
@@ -1350,13 +1302,13 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.0</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E38" s="2">
         <v>30.0</v>
@@ -1364,13 +1316,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.0</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E39" s="2">
         <v>60.0</v>
@@ -1378,13 +1330,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.0</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E40" s="5">
         <v>12.0</v>
@@ -1392,13 +1344,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2">
         <v>12.0</v>
@@ -1406,13 +1358,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.0</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2">
         <v>20.0</v>
@@ -1420,13 +1372,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.0</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2">
         <v>32.0</v>
@@ -1434,13 +1386,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.0</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E44" s="2">
         <v>80.0</v>
@@ -1448,13 +1400,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B45" s="2">
         <v>40.0</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E45" s="2">
         <v>18.0</v>
@@ -1462,13 +1414,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B46" s="2">
         <v>35.0</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E46" s="2">
         <v>40.0</v>
@@ -1476,13 +1428,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B47" s="2">
         <v>240.0</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E47" s="2">
         <v>55.0</v>
@@ -1490,13 +1442,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B48" s="2">
         <v>70.0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E48" s="2">
         <v>63.0</v>
@@ -1504,13 +1456,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B49" s="2">
         <v>30.0</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E49" s="2">
         <v>90.0</v>
@@ -1518,13 +1470,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B50" s="2">
         <v>50.0</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E50" s="2">
         <v>8.0</v>
@@ -1532,13 +1484,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B51" s="2">
         <v>75.0</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E51" s="2">
         <v>35.0</v>
@@ -1546,13 +1498,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B52" s="2">
         <v>140.0</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E52" s="2">
         <v>40.0</v>
@@ -1560,13 +1512,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B53" s="2">
         <v>140.0</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E53" s="2">
         <v>0.0</v>
@@ -1574,13 +1526,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B54" s="2">
         <v>14.0</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E54" s="2">
         <v>22.0</v>
@@ -1588,13 +1540,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B55" s="2">
         <v>45.0</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E55" s="2">
         <v>0.0</v>
@@ -1602,13 +1554,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B56" s="2">
         <v>0.0</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E56" s="2">
         <v>20.0</v>
@@ -1616,13 +1568,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2">
         <v>245.0</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E57" s="2">
         <v>29.0</v>
@@ -1630,66 +1582,66 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B58" s="2">
         <v>55.0</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B59" s="2">
         <v>56.0</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B60" s="2">
         <v>80.0</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B61" s="2">
         <v>110.0</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B62" s="2">
         <v>20.0</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E62" s="2">
         <v>260.0</v>
@@ -1697,63 +1649,63 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B63" s="2">
         <v>40.0</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B64" s="2">
         <v>195.0</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B65" s="2">
         <v>100.0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B66" s="2">
         <v>8.0</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B67" s="2">
         <v>95.0</v>
@@ -1761,7 +1713,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B68" s="2">
         <v>150.0</v>
@@ -1769,7 +1721,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B69" s="2">
         <v>-100.0</v>
@@ -1777,7 +1729,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B70" s="2">
         <v>1169.0</v>
@@ -1785,7 +1737,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B71" s="2">
         <v>34.0</v>
@@ -1793,7 +1745,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B72" s="2">
         <v>150.0</v>
@@ -1801,7 +1753,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B73" s="2">
         <v>90.0</v>
@@ -1809,7 +1761,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B74" s="2">
         <v>195.0</v>
@@ -1817,7 +1769,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B75" s="2">
         <v>0.0</v>
@@ -1825,7 +1777,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B76" s="2">
         <v>0.0</v>
@@ -1833,7 +1785,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B77" s="2">
         <v>491.0</v>
@@ -1841,7 +1793,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B78" s="2">
         <v>80.0</v>
@@ -1849,7 +1801,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B79" s="2">
         <v>43.0</v>
@@ -1857,7 +1809,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B80" s="2">
         <v>0.0</v>
@@ -1865,7 +1817,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B81" s="2">
         <v>150.0</v>
@@ -1873,7 +1825,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B82" s="2">
         <v>235.0</v>
@@ -1881,7 +1833,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B83" s="2">
         <v>28.0</v>
@@ -1889,7 +1841,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B84" s="2">
         <v>470.0</v>
@@ -1897,7 +1849,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B85" s="2">
         <v>782.0</v>
@@ -1905,7 +1857,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B86" s="2">
         <v>0.0</v>
@@ -1913,7 +1865,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B87" s="2">
         <v>300.0</v>
@@ -1921,7 +1873,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B88" s="2">
         <v>35.0</v>
@@ -1929,7 +1881,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B89" s="2">
         <v>140.0</v>
@@ -1937,7 +1889,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B90" s="2">
         <v>130.0</v>
@@ -1945,7 +1897,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B91" s="2">
         <v>89.0</v>
@@ -1953,7 +1905,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B92" s="2">
         <v>900.0</v>
@@ -1961,7 +1913,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B93" s="2">
         <v>0.0</v>
@@ -1969,7 +1921,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B94" s="2">
         <v>15.0</v>
@@ -1977,7 +1929,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B95" s="2">
         <v>33.0</v>
@@ -1985,7 +1937,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B96" s="2">
         <v>111.0</v>
@@ -1993,7 +1945,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B97" s="2">
         <v>120.0</v>
@@ -2001,7 +1953,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B98" s="2">
         <v>52.0</v>
@@ -2009,7 +1961,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B99" s="2">
         <v>10.0</v>
@@ -2017,7 +1969,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B100" s="2">
         <v>540.0</v>
@@ -2025,7 +1977,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B101" s="2">
         <v>98.0</v>
@@ -2033,7 +1985,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B102" s="2">
         <v>235.0</v>
@@ -2041,7 +1993,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B103" s="2">
         <v>345.0</v>
@@ -2049,7 +2001,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B104" s="2">
         <v>250.0</v>
